--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_magallanes.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:41</t>
+    <t xml:space="preserve">2026-09-24 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -991,7 +991,7 @@
         <v>-0.75</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1.37</v>
@@ -1014,7 +1014,7 @@
         <v>-0.23</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.14</v>
@@ -1037,7 +1037,7 @@
         <v>-0.64</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>1.21</v>
@@ -1051,16 +1051,16 @@
         <v>29</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0.78</v>
@@ -1097,19 +1097,19 @@
         <v>35</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.23</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="26">
@@ -1120,19 +1120,19 @@
         <v>35</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="27">
@@ -1143,19 +1143,19 @@
         <v>35</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.15</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.13</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="28">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_magallanes.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:31</t>
+    <t xml:space="preserve">2026-10-01 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_magallanes.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:16</t>
+    <t xml:space="preserve">2026-10-05 19:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
